--- a/datasets/pco/03 Novedades de nómina sintéticas.xlsx
+++ b/datasets/pco/03 Novedades de nómina sintéticas.xlsx
@@ -2980,7 +2980,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DATOS 100 % FICTICIOS para el programa IA-abilities (Coknow). No corresponden a la Compañía ni a ninguna persona real.</t>
+          <t>DATOS 100 % FICTICIOS para el programa IA-abilities. No corresponden a la Compañía ni a ninguna persona real.</t>
         </is>
       </c>
     </row>

--- a/datasets/pco/03 Novedades de nómina sintéticas.xlsx
+++ b/datasets/pco/03 Novedades de nómina sintéticas.xlsx
@@ -508,7 +508,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -626,7 +625,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -864,7 +862,6 @@
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -942,7 +939,6 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>No</t>
@@ -1020,7 +1016,6 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1178,7 +1173,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1296,13 +1290,11 @@
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1370,7 +1362,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1448,7 +1439,6 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1486,7 +1476,6 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1564,7 +1553,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1602,7 +1590,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1640,7 +1627,6 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1678,7 +1664,6 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1716,7 +1701,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1794,7 +1778,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1832,7 +1815,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1870,7 +1852,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1908,7 +1889,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2026,7 +2006,6 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2304,7 +2283,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2382,7 +2360,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2460,7 +2437,6 @@
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2498,7 +2474,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2576,7 +2551,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2654,7 +2628,6 @@
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2692,7 +2665,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2730,7 +2702,6 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2768,7 +2739,6 @@
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2806,7 +2776,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2971,7 +2940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2987,7 +2956,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61 novedades con 6 errores sembrados, uno por regla. Las reglas son del ejercicio, no son normativa laboral.</t>
+          <t>61 novedades de octubre. Las reglas son del ejercicio, no son normativa laboral.</t>
         </is>
       </c>
     </row>
@@ -2995,13 +2964,6 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>Uso sugerido (nivel 02, mesa de nómina): prompt de validación → reescribirlo como loop con criterios de aceptación (las 6 reglas) y condición de parada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Resultado esperado: NOV-005, NOV-012, NOV-021, NOV-034, NOV-041/NOV-061 y NOV-051.</t>
         </is>
       </c>
     </row>
